--- a/stories/arbres/ATOM-SAN.ALI.003-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dimitri joue au jardin avec papa. Le soleil chauffe le dos. Dimitri a la bouche sèche. Il a soif. Papa dit : tu as soif. Viens. Papa pose un verre sur la table du jardin. Dans le verre, il y a de l'eau. L'eau est fraîche. Dimitri prend le verre d'eau. Il boit une gorgée. Puis une autre. Papa dit : quand on a soif, on boit de l'eau. On boit dans un verre. Dimitri pose le verre. Il sent l'herbe. Plus tard, il a encore soif. Il reprend le verre. Il boit de l'eau. Papa sourit.</t>
+          <t>Dimitri joue au jardin avec papa. Le soleil chauffe le dos. Dimitri a la bouche sèche. Il a soif. Tu as soif. Viens. Papa pose un verre sur la table du jardin. Dans le verre, il y a de l'eau. L'eau est fraîche. Dimitri prend le verre d'eau. Il boit une gorgée. Puis une autre. Quand on a soif, on boit de l'eau. On boit dans un verre. Dimitri pose le verre. Il sent l'herbe. Plus tard, il a encore soif. Il reprend le verre. Il boit de l'eau. Papa sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dimitri joue au jardin avec papa. Le soleil chauffe le dos. Dimitri a la bouche sèche. Il a soif.
+papa|Tu as soif. Viens. Papa pose un verre sur la table du jardin.
+narrateur|Dans le verre, il y a de l'eau. L'eau est fraîche. Dimitri prend le verre d'eau. Il boit une gorgée. Puis une autre.
+papa|Quand on a soif, on boit de l'eau. On boit dans un verre.
+narrateur|Dimitri pose le verre. Il sent l'herbe. Plus tard, il a encore soif. Il reprend le verre. Il boit de l'eau. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Dimitri a soif. Que boit-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dimitri a eu soif. Il a pris le verre. Il a bu de l'eau. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dimitri pose le verre. Papa range la table.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Dimitri pose le verre. Il sent l'herbe. Plus tard, il a encore soif. Il reprend le verre. Il boit de l'eau. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Dimitri a soif. Que boit-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Dimitri a eu soif. Il a pris le verre. Il a bu de l'eau. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Dimitri pose le verre. Papa range la table.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.003-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dimitri boit un verre d'eau</t>
+          <t>Le verre à l'ombre</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'ombre de l'arbre bouge. Aniss a couru. Papa pose un verre à l'ombre. Aniss boit. Plus tard, il reprend de l'eau.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dimitri joue au jardin avec papa. Le soleil chauffe le dos. Dimitri a la bouche sèche. Il a soif. Tu as soif. Viens. Papa pose un verre sur la table du jardin. Dans le verre, il y a de l'eau. L'eau est fraîche. Dimitri prend le verre d'eau. Il boit une gorgée. Puis une autre. Quand on a soif, on boit de l'eau. On boit dans un verre. Dimitri pose le verre. Il sent l'herbe. Plus tard, il a encore soif. Il reprend le verre. Il boit de l'eau. Papa sourit.</t>
+          <t>Une cigale chante, tout loin. La table en bois est encore tiède. L'ombre de l'arbre bouge. Une abeille va de fleur en fleur. Elle fait un petit bourdon. Aniss vit ici, avec papa et maman. La maison est juste derrière. L'herbe sent le soleil. Aniss a couru autour du cerisier. Ses joues sont rouges. Sa bouche est sèche. Papa, j'ai soif. Tu as soif, Aniss ? Viens. Il y a de l'eau, à l'ombre. Papa pose un verre sur la table. La table est à l'ombre. Dans le verre, l'eau est claire. Une feuille danse au-dessus. Tu t'assois un moment ? Aniss tire la chaise de jardin. L'herbe chatouille ses chevilles. Il s'assoit près de papa. Il pose les pieds par terre. Bravo, Aniss. Tu es bien assis. Tu prends le verre ? Aniss prend le verre d'eau. Le verre est un peu froid. Il boit une gorgée. Puis une autre. C'est frais, papa. Oui. Quand on a soif, on boit de l'eau. On boit dans un verre. Bravo. Aniss repose le verre. Il sent l'herbe. Tu as entendu l'abeille ? Elle bourdonne. Tu te sens mieux ? Oui. Ma bouche n'est plus sèche. Plus tard, le soleil tape encore. Aniss a encore soif. Papa, encore de l'eau ? Oui. Le verre est là. Aniss reprend le verre. Il boit de l'eau. Bravo, Aniss. Tu as repris de l'eau. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,66 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Dimitri joue au jardin avec papa. Le soleil chauffe le dos. Dimitri a la bouche sèche. Il a soif.
-papa|Tu as soif. Viens. Papa pose un verre sur la table du jardin.
-narrateur|Dans le verre, il y a de l'eau. L'eau est fraîche. Dimitri prend le verre d'eau. Il boit une gorgée. Puis une autre.
-papa|Quand on a soif, on boit de l'eau. On boit dans un verre.
-narrateur|Dimitri pose le verre. Il sent l'herbe. Plus tard, il a encore soif. Il reprend le verre. Il boit de l'eau. Papa sourit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une cigale chante, tout loin.
+narrateur|La table en bois est encore tiède.
+narrateur|L'ombre de l'arbre bouge.
+narrateur|Une abeille va de fleur en fleur.
+narrateur|Elle fait un petit bourdon.
+narrateur|Aniss vit ici, avec papa et maman.
+narrateur|La maison est juste derrière.
+narrateur|L'herbe sent le soleil.
+narrateur|Aniss a couru autour du cerisier.
+narrateur|Ses joues sont rouges.
+narrateur|Sa bouche est sèche.
+enfant-m|Papa, j'ai soif.
+papa|Tu as soif, Aniss ?
+papa|Viens.
+papa|Il y a de l'eau, à l'ombre.
+narrateur|Papa pose un verre sur la table.
+narrateur|La table est à l'ombre.
+narrateur|Dans le verre, l'eau est claire.
+narrateur|Une feuille danse au-dessus.
+papa|Tu t'assois un moment ?
+narrateur|Aniss tire la chaise de jardin.
+narrateur|L'herbe chatouille ses chevilles.
+narrateur|Il s'assoit près de papa.
+narrateur|Il pose les pieds par terre.
+papa|Bravo, Aniss.
+papa|Tu es bien assis.
+papa|Tu prends le verre ?
+narrateur|Aniss prend le verre d'eau.
+narrateur|Le verre est un peu froid.
+narrateur|Il boit une gorgée.
+narrateur|Puis une autre.
+enfant-m|C'est frais, papa.
+papa|Oui.
+papa|Quand on a soif, on boit de l'eau.
+papa|On boit dans un verre.
+papa|Bravo.
+narrateur|Aniss repose le verre.
+narrateur|Il sent l'herbe.
+papa|Tu as entendu l'abeille ?
+enfant-m|Elle bourdonne.
+papa|Tu te sens mieux ?
+enfant-m|Oui.
+enfant-m|Ma bouche n'est plus sèche.
+narrateur|Plus tard, le soleil tape encore.
+narrateur|Aniss a encore soif.
+enfant-m|Papa, encore de l'eau ?
+papa|Oui.
+papa|Le verre est là.
+narrateur|Aniss reprend le verre.
+narrateur|Il boit de l'eau.
+papa|Bravo, Aniss.
+papa|Tu as repris de l'eau.
+papa|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>abeille,verre</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1413,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Dimitri a soif. Que boit-il ?</t>
+          <t>Aniss a soif. Que boit-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Dimitri a soif. Que boit-il ?</t>
+          <t>narrateur|Aniss a soif.
+narrateur|Que boit-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dimitri a eu soif. Il a pris le verre. Il a bu de l'eau. Papa était là.</t>
+          <t>Aniss a eu soif. Il a pris le verre. Il a bu de l'eau. Tu as bu de l'eau ? Oui, papa. Dans le verre. Bravo, Aniss. Quand on a soif, on boit de l'eau. Le verre reste à l'ombre. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1746,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Dimitri a eu soif. Il a pris le verre. Il a bu de l'eau. Papa était là.</t>
+          <t>narrateur|Aniss a eu soif.
+narrateur|Il a pris le verre.
+narrateur|Il a bu de l'eau.
+papa|Tu as bu de l'eau ?
+enfant-m|Oui, papa.
+enfant-m|Dans le verre.
+papa|Bravo, Aniss.
+papa|Quand on a soif, on boit de l'eau.
+narrateur|Le verre reste à l'ombre.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Dimitri pose le verre. Papa range la table.</t>
+          <t>Aniss pose le verre. Papa range la table du jardin. On reste encore un peu ? Oui. L'ombre a bougé un peu. La cigale chante encore. Ça sent l'herbe, hein ? Oui. Et l'eau était froide. Merci, Aniss. Merci, papa. Tu as bien bu. Bravo. La maison attend, tout près. Le jardin est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1923,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Dimitri pose le verre. Papa range la table.</t>
+          <t>narrateur|Aniss pose le verre.
+narrateur|Papa range la table du jardin.
+papa|On reste encore un peu ?
+enfant-m|Oui.
+narrateur|L'ombre a bougé un peu.
+narrateur|La cigale chante encore.
+papa|Ça sent l'herbe, hein ?
+enfant-m|Oui.
+enfant-m|Et l'eau était froide.
+papa|Merci, Aniss.
+enfant-m|Merci, papa.
+papa|Tu as bien bu.
+papa|Bravo.
+narrateur|La maison attend, tout près.
+narrateur|Le jardin est calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1965,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'avais soif, au jardin. J'ai bu de l'eau. Bravo. Tu as fait du bon travail. On était à l'ombre, ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2105,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'avais soif, au jardin.
+enfant-m|J'ai bu de l'eau.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+papa|On était à l'ombre, ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-07.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une cigale chante, tout loin. La table en bois est encore tiède. L'ombre de l'arbre bouge. Une abeille va de fleur en fleur. Elle fait un petit bourdon. Aniss vit ici, avec papa et maman. La maison est juste derrière. L'herbe sent le soleil. Aniss a couru autour du cerisier. Ses joues sont rouges. Sa bouche est sèche. Papa, j'ai soif. Tu as soif, Aniss ? Viens. Il y a de l'eau, à l'ombre. Papa pose un verre sur la table. La table est à l'ombre. Dans le verre, l'eau est claire. Une feuille danse au-dessus. Tu t'assois un moment ? Aniss tire la chaise de jardin. L'herbe chatouille ses chevilles. Il s'assoit près de papa. Il pose les pieds par terre. Bravo, Aniss. Tu es bien assis. Tu prends le verre ? Aniss prend le verre d'eau. Le verre est un peu froid. Il boit une gorgée. Puis une autre. C'est frais, papa. Oui. Quand on a soif, on boit de l'eau. On boit dans un verre. Bravo. Aniss repose le verre. Il sent l'herbe. Tu as entendu l'abeille ? Elle bourdonne. Tu te sens mieux ? Oui. Ma bouche n'est plus sèche. Plus tard, le soleil tape encore. Aniss a encore soif. Papa, encore de l'eau ? Oui. Le verre est là. Aniss reprend le verre. Il boit de l'eau. Bravo, Aniss. Tu as repris de l'eau. C'est du bon travail.</t>
+          <t>Une cigale chante, tout loin. La table en bois est encore tiède. L'ombre de l'arbre bouge. Une abeille va de fleur en fleur. Elle fait un petit bourdon. Aniss vit ici, avec papa et maman. La maison est juste derrière. L'herbe sent le soleil. Aniss a couru autour du cerisier. Ses joues sont rouges. Sa bouche est sèche. Papa, j'ai soif. Tu as soif, Aniss ? Viens. Il y a de l'eau, à l'ombre. Papa pose un verre sur la table. La table est à l'ombre. Dans le verre, l'eau est claire. Une feuille danse au-dessus. Tu t'assois un moment ? Aniss tire la chaise de jardin. L'herbe chatouille ses chevilles. Il s'assoit près de papa. Il pose les pieds par terre. Bravo, Aniss. Tu es bien assis. Tu prends le verre ? Aniss prend le verre d'eau. Le verre est un peu froid. Il boit une gorgée. Puis une autre. C'est frais, papa. Oui. Quand on a soif, on boit de l'eau. On boit dans un verre. Bravo. Aniss repose le verre. Il sent l'herbe. Tu as entendu l'abeille ? Elle bourdonne. Tu te sens mieux ? Oui. Ma bouche n'est plus sèche. Plus tard, le soleil tape encore. Aniss a encore soif. Papa, encore de l'eau ? Oui. Le verre est là. Aniss reprend le verre. Il boit de l'eau. Bravo, Aniss. Tu as repris de l'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dimitri joue au jardin avec papa. Le soleil chauffe le dos. Dimitri a la bouche sèche. Il a soif. Papa dit : tu as soif. Viens. Papa pose un verre sur la table du jardin. Dans le verre, il y a de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. L'eau est fraîche. Dimitri prend le verre d'eau. Il boit une gorgée. Puis une autre. Papa dit : quand on a soif, on boit de l'eau. On boit dans un verre. Dimitri pose le verre. Il sent l'herbe. Plus tard, il a encore soif. Il reprend le verre. Il boit de l'eau. Papa sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une cigale chante, tout loin. La table en bois est encore tiède. L'ombre de l'arbre bouge. Une abeille va de fleur en fleur. Elle fait un petit bourdon. Aniss vit ici, avec papa et maman. La maison est juste derrière. L'herbe sent le soleil. Aniss a couru autour du cerisier. Ses joues sont rouges. Sa bouche est sèche. Papa, j'ai soif. Tu as soif, Aniss ? Viens. Il y a de l'eau, à l'ombre. Papa pose un verre sur la table. La table est à l'ombre. Dans le verre, l'eau est claire. Une feuille danse au-dessus. Tu t'assois un moment ? Aniss tire la chaise de jardin. L'herbe chatouille ses chevilles. Il s'assoit près de papa. Il pose les pieds par terre. Bravo, Aniss. Tu es bien assis. Tu prends le verre ? Aniss prend le verre d'eau. Le verre est un peu froid. Il boit une gorgée. Puis une autre. C'est frais, papa. Oui. Quand on a soif, on boit de l'eau. On boit dans un verre. Bravo. Aniss repose le verre. Il sent l'herbe. Tu as entendu l'abeille ? Elle bourdonne. Tu te sens mieux ? Oui. Ma bouche n'est plus sèche. Plus tard, le soleil tape encore. Aniss a encore soif. Papa, encore de l'eau ? Oui. Le verre est là. Aniss reprend le verre. Il boit de l'eau. Bravo, Aniss. Tu as repris de l'eau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1380,8 +1380,7 @@
 narrateur|Aniss reprend le verre.
 narrateur|Il boit de l'eau.
 papa|Bravo, Aniss.
-papa|Tu as repris de l'eau.
-papa|C'est du bon travail.</t>
+papa|Tu as repris de l'eau.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1418,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Dimitri a &lt;emphasis level="moderate"&gt;soif&lt;/emphasis&gt;. Que boit-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a soif. Que boit-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1577,7 +1576,6 @@
 narrateur|Que boit-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1602,12 +1600,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a eu soif. Il a pris le verre. Il a bu de l'eau. Tu as bu de l'eau ? Oui, papa. Dans le verre. Bravo, Aniss. Quand on a soif, on boit de l'eau. Le verre reste à l'ombre. Tu as fait du bon travail.</t>
+          <t>Aniss a eu soif. Il a pris le verre. Il a bu de l'eau. Tu as bu de l'eau ? Oui, papa. Dans le verre. Bravo, Aniss. Quand on a soif, on boit de l'eau. Le verre reste à l'ombre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dimitri a eu soif. Il a pris le verre. Il a bu de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a eu soif. Il a pris le verre. Il a bu de l'eau. Tu as bu de l'eau ? Oui, papa. Dans le verre. Bravo, Aniss. Quand on a soif, on boit de l'eau. Le verre reste à l'ombre.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1754,11 +1752,9 @@
 enfant-m|Dans le verre.
 papa|Bravo, Aniss.
 papa|Quand on a soif, on boit de l'eau.
-narrateur|Le verre reste à l'ombre.
-papa|Tu as fait du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+narrateur|Le verre reste à l'ombre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1788,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dimitri pose le &lt;emphasis level="moderate"&gt;verre&lt;/emphasis&gt;. Papa range la table.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss pose le verre. Papa range la table du jardin. On reste encore un peu ? Oui. L'ombre a bougé un peu. La cigale chante encore. Ça sent l'herbe, hein ? Oui. Et l'eau était froide. Merci, Aniss. Merci, papa. Tu as bien bu. Bravo. La maison attend, tout près. Le jardin est calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1940,7 +1936,6 @@
 narrateur|Le jardin est calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'avais soif, au jardin. J'ai bu de l'eau. Bravo. Tu as fait du bon travail. On était à l'ombre, ensemble. L'histoire est finie.</t>
+          <t>J'avais soif, au jardin. J'ai bu de l'eau. Bravo. On était à l'ombre, ensemble.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'avais soif, au jardin. J'ai bu de l'eau. Bravo. On était à l'ombre, ensemble.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,12 +2103,9 @@
           <t>enfant-m|J'avais soif, au jardin.
 enfant-m|J'ai bu de l'eau.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-papa|On était à l'ombre, ensemble.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|On était à l'ombre, ensemble.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2132,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-07.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dimitri, papa</t>
+          <t>Aniss, papa</t>
         </is>
       </c>
     </row>
